--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2302-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2302-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2DD3EEAF-9A36-4F75-9616-0A4CD5D9F70C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE892CD5-8EF6-4AD8-80CC-7465819444E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{DB779909-A01B-4AC6-B18D-9F09F60412D3}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{ED890024-B286-4451-85DA-AE68348D73E3}"/>
   </bookViews>
   <sheets>
     <sheet name="2302-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1445,29 +1445,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FCC4CDA-EF03-46BF-85B4-92A853745F2F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5228FB27-7BF9-4FB4-99A8-4BE7C64E9686}">
   <dimension ref="A1:X45"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1501,7 +1500,7 @@
       <c r="W1" s="27"/>
       <c r="X1" s="19"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1537,7 +1536,7 @@
       <c r="W2" s="29"/>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1589,7 +1588,7 @@
       </c>
       <c r="X3" s="33"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1657,7 +1656,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>2024</v>
       </c>
@@ -1729,7 +1728,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="36">
         <v>2023</v>
       </c>
@@ -1801,7 +1800,7 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>2022</v>
       </c>
@@ -1873,7 +1872,7 @@
         <v>5.18</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="36">
         <v>2021</v>
       </c>
@@ -1945,7 +1944,7 @@
         <v>4.25</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>2020</v>
       </c>
@@ -2017,7 +2016,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2019</v>
       </c>
@@ -2089,7 +2088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>2018</v>
       </c>
@@ -2161,7 +2160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2017</v>
       </c>
@@ -2233,7 +2232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>2016</v>
       </c>
@@ -2305,7 +2304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2015</v>
       </c>
@@ -2377,7 +2376,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>2014</v>
       </c>
@@ -2449,7 +2448,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2013</v>
       </c>
@@ -2521,7 +2520,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>2012</v>
       </c>
@@ -2593,7 +2592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2011</v>
       </c>
@@ -2665,7 +2664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>2010</v>
       </c>
@@ -2737,7 +2736,7 @@
         <v>6.43</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2009</v>
       </c>
@@ -2809,7 +2808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <v>2008</v>
       </c>
@@ -2881,7 +2880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2007</v>
       </c>
@@ -2953,7 +2952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="34">
         <v>2006</v>
       </c>
@@ -3025,7 +3024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>2005</v>
       </c>
@@ -3097,7 +3096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="34">
         <v>2004</v>
       </c>
@@ -3169,7 +3168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2003</v>
       </c>
@@ -3241,7 +3240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="34">
         <v>2002</v>
       </c>
@@ -3313,7 +3312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2001</v>
       </c>
@@ -3385,7 +3384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="34">
         <v>2000</v>
       </c>
@@ -3457,7 +3456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>1999</v>
       </c>
@@ -3529,7 +3528,7 @@
         <v>41.1</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="34">
         <v>1998</v>
       </c>
@@ -3601,7 +3600,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>1997</v>
       </c>
@@ -3673,7 +3672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="34">
         <v>1996</v>
       </c>
@@ -3745,7 +3744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="36">
         <v>1995</v>
       </c>
@@ -3817,7 +3816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="34">
         <v>1994</v>
       </c>
@@ -3889,7 +3888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="36">
         <v>1993</v>
       </c>
@@ -3961,7 +3960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="34">
         <v>1992</v>
       </c>
@@ -4033,7 +4032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="36">
         <v>1991</v>
       </c>
@@ -4105,7 +4104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="34">
         <v>1990</v>
       </c>
@@ -4177,7 +4176,7 @@
         <v>6.12</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="36">
         <v>1989</v>
       </c>
@@ -4249,7 +4248,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="34">
         <v>1987</v>
       </c>
@@ -4321,7 +4320,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="36">
         <v>1986</v>
       </c>
@@ -4393,7 +4392,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="34">
         <v>1984</v>
       </c>
@@ -4465,7 +4464,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="36">
         <v>1983</v>
       </c>
@@ -4537,7 +4536,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="34" t="s">
         <v>40</v>
       </c>
